--- a/Data/Submission/mountains_enriched_ВоленбовськийГВ.xlsx
+++ b/Data/Submission/mountains_enriched_ВоленбовськийГВ.xlsx
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1524</v>
+        <v>3108</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Submission/mountains_enriched_ВоленбовськийГВ.xlsx
+++ b/Data/Submission/mountains_enriched_ВоленбовськийГВ.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="enrichment_log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="звірка_з_еталоном" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -387,7 +388,7 @@
           <t>Nepal/China</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="0" t="n">
         <v>8848.860000000001</v>
       </c>
     </row>
@@ -402,7 +403,7 @@
           <t>Pakistan/China</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="0" t="n">
         <v>8611</v>
       </c>
     </row>
@@ -417,7 +418,7 @@
           <t>Nepal/India</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="0" t="n">
         <v>8586</v>
       </c>
     </row>
@@ -432,7 +433,7 @@
           <t>Nepal/China</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="0" t="n">
         <v>8516</v>
       </c>
     </row>
@@ -447,7 +448,7 @@
           <t>Nepal/China</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="0" t="n">
         <v>8485</v>
       </c>
     </row>
@@ -462,7 +463,7 @@
           <t>Nepal/China</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>8188</v>
       </c>
     </row>
@@ -477,7 +478,7 @@
           <t>Nepal</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="0" t="n">
         <v>8167</v>
       </c>
     </row>
@@ -492,7 +493,7 @@
           <t>Nepal</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="0" t="n">
         <v>8163</v>
       </c>
     </row>
@@ -507,7 +508,7 @@
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="0" t="n">
         <v>8126</v>
       </c>
     </row>
@@ -522,7 +523,7 @@
           <t>Nepal</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="0" t="n">
         <v>8091</v>
       </c>
     </row>
@@ -1598,523 +1599,774 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>8848.860000000001</v>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>meters</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>wikidata_lookup</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q513</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>wikidata P2044 / Mount Everest</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>8611</v>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>meters</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>wikidata_lookup</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q43512</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>wikidata P2044 / K2</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>[wikidata_lookup] Назва «K2» неоднозначна; інші кандидати: 3253 (Q872294); підтверджено через llm_knowledge</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>3108</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>8586</v>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>meters</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>wikidata_lookup</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q82019</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>wikidata P2044 / Kangchenjunga</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
+          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
+        </is>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>8516</v>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>meters</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>wikidata_lookup</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q168702</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>wikidata P2044 / Lhotse</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
+        </is>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>8485</v>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>meters</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>wikidata_lookup</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q169986</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>wikidata P2044 / Makalu</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>8188</v>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>meters</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>wikidata_lookup</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q170089</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>wikidata P2044 / Cho Oyu</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>8167</v>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>meters</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>wikidata_lookup</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q165440</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>wikidata P2044 / Dhaulagiri</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>8163</v>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>meters</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>wikidata_lookup</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q170070</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>wikidata P2044 / Manaslu</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>8126</v>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>meters</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>wikidata_lookup</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q130736</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>wikidata P2044 / Nanga Parbat</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>8091</v>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>meters</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>wikidata_lookup</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q16466024</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>wikidata P2044 / Annapurna</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="4" min="1" max="1"/>
+    <col width="12" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="15" customWidth="1" style="4" min="4" max="4"/>
+    <col width="16" customWidth="1" style="4" min="5" max="5"/>
+    <col width="46" customWidth="1" style="4" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>рядок</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>еталон</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>наше значення</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>відхилення, %</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>вердикт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
+      <c r="B2" t="n">
+        <v>8849</v>
       </c>
       <c r="C2" t="n">
         <v>8848.860000000001</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>meters</t>
-        </is>
+      <c r="D2" t="n">
+        <v>-0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>wikidata_lookup</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>http://www.wikidata.org/entity/Q513</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>wikidata P2044 / Mount Everest</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>31</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>3</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
+      <c r="B3" t="n">
+        <v>8611</v>
       </c>
       <c r="C3" t="n">
         <v>8611</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>meters</t>
-        </is>
+      <c r="D3" t="n">
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>wikidata_lookup</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>http://www.wikidata.org/entity/Q43512</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>wikidata P2044 / K2</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>[wikidata_lookup] Назва «K2» неоднозначна; інші кандидати: 3253 (Q872294); підтверджено через llm_knowledge</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>3108</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>4</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
+      <c r="B4" t="n">
+        <v>8586</v>
       </c>
       <c r="C4" t="n">
         <v>8586</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>meters</t>
-        </is>
+      <c r="D4" t="n">
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>wikidata_lookup</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>http://www.wikidata.org/entity/Q82019</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>wikidata P2044 / Kangchenjunga</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>38</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>5</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
+      <c r="B5" t="n">
+        <v>8516</v>
       </c>
       <c r="C5" t="n">
         <v>8516</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>meters</t>
-        </is>
+      <c r="D5" t="n">
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>wikidata_lookup</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>http://www.wikidata.org/entity/Q168702</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>wikidata P2044 / Lhotse</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>32</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>6</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
+      <c r="B6" t="n">
+        <v>8485</v>
       </c>
       <c r="C6" t="n">
         <v>8485</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>meters</t>
-        </is>
+      <c r="D6" t="n">
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>wikidata_lookup</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>http://www.wikidata.org/entity/Q169986</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>wikidata P2044 / Makalu</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>36</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>7</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
+      <c r="B7" t="n">
+        <v>8188</v>
       </c>
       <c r="C7" t="n">
         <v>8188</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>meters</t>
-        </is>
+      <c r="D7" t="n">
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>wikidata_lookup</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>http://www.wikidata.org/entity/Q170089</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>wikidata P2044 / Cho Oyu</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>41</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>8</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
+      <c r="B8" t="n">
+        <v>8167</v>
       </c>
       <c r="C8" t="n">
         <v>8167</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>meters</t>
-        </is>
+      <c r="D8" t="n">
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>wikidata_lookup</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>http://www.wikidata.org/entity/Q165440</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>wikidata P2044 / Dhaulagiri</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>40</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>9</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
+      <c r="B9" t="n">
+        <v>8163</v>
       </c>
       <c r="C9" t="n">
         <v>8163</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>meters</t>
-        </is>
+      <c r="D9" t="n">
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>wikidata_lookup</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>http://www.wikidata.org/entity/Q170070</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>wikidata P2044 / Manaslu</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>33</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>10</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
+      <c r="B10" t="n">
+        <v>8215</v>
       </c>
       <c r="C10" t="n">
         <v>8126</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>meters</t>
-        </is>
+      <c r="D10" t="n">
+        <v>-1.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>wikidata_lookup</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>http://www.wikidata.org/entity/Q130736</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wikidata P2044 / Nanga Parbat</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>21</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>11</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
+      <c r="B11" t="n">
+        <v>8091</v>
       </c>
       <c r="C11" t="n">
         <v>8091</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>meters</t>
-        </is>
+      <c r="D11" t="n">
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>wikidata_lookup</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>http://www.wikidata.org/entity/Q16466024</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>wikidata P2044 / Annapurna</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>[wikidata_lookup] Структуроване джерело Wikidata</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>18</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>У допуску ±10%</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10 з 10</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Data/Submission/mountains_enriched_ВоленбовськийГВ.xlsx
+++ b/Data/Submission/mountains_enriched_ВоленбовськийГВ.xlsx
@@ -1521,20 +1521,6 @@
   </sheetPr>
   <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16" customWidth="1" style="4" min="2" max="2"/>
-    <col width="12" customWidth="1" style="4" min="3" max="3"/>
-    <col width="8" customWidth="1" style="4" min="4" max="4"/>
-    <col width="20" customWidth="1" style="4" min="5" max="5"/>
-    <col width="46" customWidth="1" style="4" min="6" max="6"/>
-    <col width="40" customWidth="1" style="4" min="7" max="7"/>
-    <col width="8" customWidth="1" style="4" min="8" max="8"/>
-    <col width="14" customWidth="1" style="4" min="9" max="9"/>
-    <col width="60" customWidth="1" style="4" min="10" max="10"/>
-    <col width="12" customWidth="1" style="4" min="11" max="11"/>
-    <col width="10" customWidth="1" style="4" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
@@ -1644,7 +1630,7 @@
         </is>
       </c>
       <c r="K2" s="0" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L2" s="0" t="n">
         <v>0</v>
@@ -1692,11 +1678,11 @@
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «K2» неоднозначна; інші кандидати: 3253 (Q872294); підтверджено через llm_knowledge</t>
+          <t>[wikidata_lookup] Назва «K2» неоднозначна; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K3" s="0" t="n">
-        <v>3108</v>
+        <v>0</v>
       </c>
       <c r="L3" s="0" t="n">
         <v>0</v>
@@ -1748,7 +1734,7 @@
         </is>
       </c>
       <c r="K4" s="0" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L4" s="0" t="n">
         <v>0</v>
@@ -1800,7 +1786,7 @@
         </is>
       </c>
       <c r="K5" s="0" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L5" s="0" t="n">
         <v>0</v>
@@ -1852,7 +1838,7 @@
         </is>
       </c>
       <c r="K6" s="0" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L6" s="0" t="n">
         <v>0</v>
@@ -1904,7 +1890,7 @@
         </is>
       </c>
       <c r="K7" s="0" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L7" s="0" t="n">
         <v>0</v>
@@ -1956,7 +1942,7 @@
         </is>
       </c>
       <c r="K8" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L8" s="0" t="n">
         <v>0</v>
@@ -2008,7 +1994,7 @@
         </is>
       </c>
       <c r="K9" s="0" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L9" s="0" t="n">
         <v>0</v>
@@ -2060,7 +2046,7 @@
         </is>
       </c>
       <c r="K10" s="0" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L10" s="0" t="n">
         <v>0</v>
@@ -2112,7 +2098,7 @@
         </is>
       </c>
       <c r="K11" s="0" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L11" s="0" t="n">
         <v>0</v>
